--- a/s.xlsx
+++ b/s.xlsx
@@ -13,6 +13,14 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>abc</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
@@ -31,70 +39,69 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -106,9 +113,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -116,21 +123,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -147,28 +139,44 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -183,6 +191,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -195,13 +257,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -213,157 +311,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,32 +385,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -431,26 +433,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -460,6 +453,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -479,148 +487,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -947,9 +955,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5"/>
-  <sheetData/>
+  <dimension ref="A6"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelRow="5"/>
+  <sheetData>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
